--- a/reports/pdf_rolling5_20261028.xlsx
+++ b/reports/pdf_rolling5_20261028.xlsx
@@ -536,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K116"/>
+  <dimension ref="A1:K144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -562,14 +562,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-10-21 ~ 2026-10-28  (최근 5거래일)  ·  캡처 6/10  ·  대기: RISE, TIGER, TIGER, MIDAS</t>
+          <t>최근 5거래일 변화  ·  2026-10-21 ~ 2026-10-28  (최근 5거래일)  ·  캡처 9/10  ·  대기: RISE</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,121억   ·   현금 -6억(-0.1%)      오늘 2026-10-28  vs  5일전 2026-10-21      매수 13종목  /  매도 10종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,313억      오늘 2026-10-28  vs  5일전 2026-10-21      매수 13종목  /  매도 10종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -665,7 +665,7 @@
         <v>314</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>2600429047</v>
+        <v>2600429937</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         <v>-82</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-4999557105</v>
+        <v>-4999558817</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>224</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>4615464651</v>
+        <v>4615466231</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>-72</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-681356976</v>
+        <v>-681357209</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         <v>170</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>4439703626</v>
+        <v>4439705146</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
         <v>-69</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-2970212369</v>
+        <v>-2970213386</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>92</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>6961328181</v>
+        <v>6961330565</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>-46</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-2119459499</v>
+        <v>-2119460225</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>76</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>2033862887</v>
+        <v>2033863583</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
         <v>-33</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-891316926</v>
+        <v>-891317231</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>71</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>3451122337</v>
+        <v>3451123518</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>-16</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-4130880582</v>
+        <v>-4130881997</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>52</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1179882766</v>
+        <v>1179883170</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>-11</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-1652650133</v>
+        <v>-1652650699</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>29</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>1176357616</v>
+        <v>1176358019</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>-6</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-115644796</v>
+        <v>-115644836</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>25</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1261110178</v>
+        <v>1261110610</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>-5</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-983566639</v>
+        <v>-983566975</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1054,23 +1054,23 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>파크시스템스</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>2687058379</v>
+        <v>571968276</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>1.43%→1.92%</t>
+          <t>0.40%→0.51%</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>25→37</t>
+          <t>34→46</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -1082,7 +1082,7 @@
         <v>-4</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-846036119</v>
+        <v>-846036409</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1098,23 +1098,23 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>파크시스템스</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>571968081</v>
+        <v>2687059299</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>0.40%→0.51%</t>
+          <t>1.43%→1.92%</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>34→46</t>
+          <t>25→37</t>
         </is>
       </c>
       <c r="G16" s="17" t="n"/>
@@ -1133,7 +1133,7 @@
         <v>9</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>1952734775</v>
+        <v>1952735444</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>8</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>719726501</v>
+        <v>719726748</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
     <row r="20" ht="19" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 2,996억   ·   현금 62억(2.1%)      오늘 2026-10-28  vs  5일전 2026-10-21      매수 8종목  /  매도 16종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 2,932억      오늘 2026-10-28  vs  5일전 2026-10-21      매수 8종목  /  매도 16종목</t>
         </is>
       </c>
       <c r="B20" s="4" t="n"/>
@@ -1278,7 +1278,7 @@
         <v>141</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>2964319446</v>
+        <v>2964319777</v>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>-118</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-1428902768</v>
+        <v>-1428902927</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>104</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>4467838336</v>
+        <v>4467838835</v>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>-113</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-2475783878</v>
+        <v>-2475784155</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>65</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1425868719</v>
+        <v>1425868878</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>-58</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-1191334056</v>
+        <v>-1191334189</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>39</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>1568630116</v>
+        <v>1568630291</v>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>-43</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-5045381621</v>
+        <v>-5045382185</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>13</v>
       </c>
       <c r="C27" s="11" t="n">
-        <v>901246764</v>
+        <v>901246865</v>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>-38</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-1848782911</v>
+        <v>-1848783118</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>12</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>8854052702</v>
+        <v>8854053692</v>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>-33</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-1132371478</v>
+        <v>-1132371605</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         <v>9</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>911503461</v>
+        <v>911503562</v>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>-32</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-3082808452</v>
+        <v>-3082808796</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>6</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>148050845</v>
+        <v>148050861</v>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>-26</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-172291016</v>
+        <v>-172291035</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>-25</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>-283267394</v>
+        <v>-283267426</v>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>-24</v>
       </c>
       <c r="I32" s="15" t="n">
-        <v>-462679028</v>
+        <v>-462679079</v>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>-22</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>-949845246</v>
+        <v>-949845352</v>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
         <v>-22</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-2734939981</v>
+        <v>-2734940287</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>-18</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-142090147</v>
+        <v>-142090163</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>-7</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-1317529009</v>
+        <v>-1317529157</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>-6</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-25550450</v>
+        <v>-25550453</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>-4</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-60143978</v>
+        <v>-60143984</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
     <row r="40" ht="19" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,019억   ·   현금 40억(1.9%)      오늘 2026-10-28  vs  5일전 2026-10-21      매수 22종목  /  매도 27종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,112억      오늘 2026-10-28  vs  5일전 2026-10-21      매수 22종목  /  매도 27종목</t>
         </is>
       </c>
       <c r="B40" s="4" t="n"/>
@@ -1943,7 +1943,7 @@
         <v>995</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>6521026272</v>
+        <v>6530879136</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>-249</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-7599026290</v>
+        <v>-7610507945</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>494</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>8600830164</v>
+        <v>8613825482</v>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>-202</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-1028336814</v>
+        <v>-1029890567</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>300</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>4716746580</v>
+        <v>4723873290</v>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>-120</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-1061317630</v>
+        <v>-1062921215</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>248</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>5951375685</v>
+        <v>5960367842</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>-118</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-1024881177</v>
+        <v>-1026429708</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>194</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>4809625113</v>
+        <v>4816892156</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>-112</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-971285696</v>
+        <v>-972753248</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>151</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>1369478407</v>
+        <v>1371547604</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>-111</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-2127302358</v>
+        <v>-2130516579</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
@@ -2200,18 +2200,18 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>엘리스  (신규)</t>
+          <t>알멕  (신규)</t>
         </is>
       </c>
       <c r="B49" s="11" t="n">
         <v>150</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>8003574197</v>
+        <v>6195732757</v>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>0.00%→3.87%</t>
+          <t>0.00%→2.99%</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
@@ -2228,7 +2228,7 @@
         <v>-108</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-2538106160</v>
+        <v>-2541941080</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
@@ -2244,18 +2244,18 @@
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>알멕  (신규)</t>
+          <t>엘리스  (신규)</t>
         </is>
       </c>
       <c r="B50" s="11" t="n">
         <v>150</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>6186385514</v>
+        <v>8015667098</v>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>0.00%→2.99%</t>
+          <t>0.00%→3.87%</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
@@ -2272,7 +2272,7 @@
         <v>-106</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-7796103547</v>
+        <v>-7807882974</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>139</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>2190026812</v>
+        <v>2193335806</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>-102</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-3896131975</v>
+        <v>-3902018788</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>134</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>1947139188</v>
+        <v>1950081194</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         <v>-100</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-1860218651</v>
+        <v>-1863029326</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
@@ -2376,18 +2376,18 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>엘티씨  (신규)</t>
+          <t>디케이티  (신규)</t>
         </is>
       </c>
       <c r="B53" s="11" t="n">
         <v>99</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>2202075203</v>
+        <v>1680306592</v>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.06%</t>
+          <t>0.00%→0.81%</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
@@ -2404,7 +2404,7 @@
         <v>-97</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-1663141394</v>
+        <v>-1665654297</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
@@ -2420,18 +2420,18 @@
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>디케이티  (신규)</t>
+          <t>엘티씨  (신규)</t>
         </is>
       </c>
       <c r="B54" s="11" t="n">
         <v>99</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>1677771583</v>
+        <v>2205402402</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.81%</t>
+          <t>0.00%→1.06%</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
@@ -2448,7 +2448,7 @@
         <v>-77</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-8910248739</v>
+        <v>-8923711570</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>79</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>5705707663</v>
+        <v>5714328631</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>-75</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-3172632700</v>
+        <v>-3177426350</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>70</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>2235903379</v>
+        <v>2239281689</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>-66</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-1887493031</v>
+        <v>-1890344916</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>50</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>2234248380</v>
+        <v>2237624190</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>-60</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-6720619127</v>
+        <v>-6730773564</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>40</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>3103453750</v>
+        <v>3108142875</v>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>-50</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-3214007670</v>
+        <v>-3218863835</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>40</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>2399086260</v>
+        <v>2402711130</v>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>-44</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-2167121629</v>
+        <v>-2170396014</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
@@ -2691,7 +2691,7 @@
         <v>31</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>4484053749</v>
+        <v>4490828874</v>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>-39</v>
       </c>
       <c r="I60" s="15" t="n">
-        <v>-2421726644</v>
+        <v>-2425385722</v>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>29</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>2142495247</v>
+        <v>2145732423</v>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>-35</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>-9152143364</v>
+        <v>-9165971682</v>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>27</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>681892606</v>
+        <v>682922903</v>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>-28</v>
       </c>
       <c r="I62" s="15" t="n">
-        <v>-2009300943</v>
+        <v>-2012336872</v>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>20</v>
       </c>
       <c r="C63" s="11" t="n">
-        <v>1069791224</v>
+        <v>1071407612</v>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>-26</v>
       </c>
       <c r="I63" s="15" t="n">
-        <v>-4475116755</v>
+        <v>-4481878378</v>
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>11</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>1827780675</v>
+        <v>1830542337</v>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
@@ -2881,23 +2881,23 @@
       </c>
       <c r="G64" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>대주전자재료</t>
         </is>
       </c>
       <c r="H64" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I64" s="15" t="n">
-        <v>-1057544233</v>
+        <v>-1544789441</v>
       </c>
       <c r="J64" s="16" t="inlineStr">
         <is>
-          <t>1.23%→0.72%</t>
+          <t>1.52%→0.75%</t>
         </is>
       </c>
       <c r="K64" s="13" t="inlineStr">
         <is>
-          <t>60→35</t>
+          <t>50→25</t>
         </is>
       </c>
     </row>
@@ -2909,23 +2909,23 @@
       <c r="E65" s="17" t="n"/>
       <c r="G65" s="14" t="inlineStr">
         <is>
-          <t>대주전자재료</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H65" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I65" s="15" t="n">
-        <v>-1542458882</v>
+        <v>-1059142117</v>
       </c>
       <c r="J65" s="16" t="inlineStr">
         <is>
-          <t>1.52%→0.75%</t>
+          <t>1.23%→0.72%</t>
         </is>
       </c>
       <c r="K65" s="13" t="inlineStr">
         <is>
-          <t>50→25</t>
+          <t>60→35</t>
         </is>
       </c>
     </row>
@@ -2944,7 +2944,7 @@
         <v>-19</v>
       </c>
       <c r="I66" s="15" t="n">
-        <v>-3144497720</v>
+        <v>-3149248860</v>
       </c>
       <c r="J66" s="16" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>-15</v>
       </c>
       <c r="I67" s="15" t="n">
-        <v>-1502407911</v>
+        <v>-1504677955</v>
       </c>
       <c r="J67" s="16" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>-8</v>
       </c>
       <c r="I68" s="15" t="n">
-        <v>-1861542650</v>
+        <v>-1864355325</v>
       </c>
       <c r="J68" s="16" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>-7</v>
       </c>
       <c r="I69" s="15" t="n">
-        <v>-1232643106</v>
+        <v>-1234505553</v>
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
     <row r="71" ht="19" customHeight="1">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,079억   ·   현금 2억(0.1%)      오늘 2026-10-28  vs  5일전 2026-10-21      매수 6종목  /  매도 4종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,032억      오늘 2026-10-28  vs  5일전 2026-10-21      매수 6종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B71" s="4" t="n"/>
@@ -3140,7 +3140,7 @@
         <v>207</v>
       </c>
       <c r="C74" s="11" t="n">
-        <v>1906719250</v>
+        <v>1906718022</v>
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         <v>-228</v>
       </c>
       <c r="I74" s="15" t="n">
-        <v>-3606186407</v>
+        <v>-3606184086</v>
       </c>
       <c r="J74" s="16" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>141</v>
       </c>
       <c r="C75" s="11" t="n">
-        <v>2113365342</v>
+        <v>2113363982</v>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>-155</v>
       </c>
       <c r="I75" s="15" t="n">
-        <v>-1455915649</v>
+        <v>-1455914712</v>
       </c>
       <c r="J75" s="16" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>51</v>
       </c>
       <c r="C76" s="11" t="n">
-        <v>1866723232</v>
+        <v>1866722030</v>
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>-61</v>
       </c>
       <c r="I76" s="15" t="n">
-        <v>-1005475648</v>
+        <v>-1005475001</v>
       </c>
       <c r="J76" s="16" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
         <v>33</v>
       </c>
       <c r="C77" s="11" t="n">
-        <v>652601691</v>
+        <v>652601271</v>
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>-51</v>
       </c>
       <c r="I77" s="15" t="n">
-        <v>-788103351</v>
+        <v>-788102844</v>
       </c>
       <c r="J77" s="16" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>18</v>
       </c>
       <c r="C78" s="11" t="n">
-        <v>584669060</v>
+        <v>584668684</v>
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>7</v>
       </c>
       <c r="C79" s="11" t="n">
-        <v>533361038</v>
+        <v>533360694</v>
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
     <row r="81" ht="19" customHeight="1">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 233억   ·   현금 2억(0.9%)      오늘 2026-10-28  vs  5일전 2026-10-21      매수 6종목  /  매도 5종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 241억      오늘 2026-10-28  vs  5일전 2026-10-21      매수 6종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B81" s="4" t="n"/>
@@ -3461,7 +3461,7 @@
         <v>345</v>
       </c>
       <c r="C84" s="11" t="n">
-        <v>170457600</v>
+        <v>176640110</v>
       </c>
       <c r="D84" s="12" t="inlineStr">
         <is>
@@ -3482,11 +3482,11 @@
         <v>-67</v>
       </c>
       <c r="I84" s="15" t="n">
-        <v>-119420800</v>
+        <v>-112774470</v>
       </c>
       <c r="J84" s="16" t="inlineStr">
         <is>
-          <t>6.46%→5.92%</t>
+          <t>5.89%→5.39%</t>
         </is>
       </c>
       <c r="K84" s="13" t="inlineStr">
@@ -3505,11 +3505,11 @@
         <v>77</v>
       </c>
       <c r="C85" s="11" t="n">
-        <v>71800960</v>
+        <v>72688045</v>
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>3.30%→3.60%</t>
+          <t>3.22%→3.51%</t>
         </is>
       </c>
       <c r="E85" s="13" t="inlineStr">
@@ -3526,11 +3526,11 @@
         <v>-26</v>
       </c>
       <c r="I85" s="15" t="n">
-        <v>-68972800</v>
+        <v>-71302445</v>
       </c>
       <c r="J85" s="16" t="inlineStr">
         <is>
-          <t>2.98%→2.67%</t>
+          <t>2.98%→2.66%</t>
         </is>
       </c>
       <c r="K85" s="13" t="inlineStr">
@@ -3549,11 +3549,11 @@
         <v>45</v>
       </c>
       <c r="C86" s="11" t="n">
-        <v>90288000</v>
+        <v>86400054</v>
       </c>
       <c r="D86" s="12" t="inlineStr">
         <is>
-          <t>7.09%→7.45%</t>
+          <t>6.55%→6.88%</t>
         </is>
       </c>
       <c r="E86" s="13" t="inlineStr">
@@ -3570,11 +3570,11 @@
         <v>-24</v>
       </c>
       <c r="I86" s="15" t="n">
-        <v>-79718400</v>
+        <v>-88627255</v>
       </c>
       <c r="J86" s="16" t="inlineStr">
         <is>
-          <t>4.62%→4.25%</t>
+          <t>4.95%→4.56%</t>
         </is>
       </c>
       <c r="K86" s="13" t="inlineStr">
@@ -3593,11 +3593,11 @@
         <v>10</v>
       </c>
       <c r="C87" s="11" t="n">
-        <v>37184000</v>
+        <v>39552025</v>
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
-          <t>1.02%→1.18%</t>
+          <t>1.05%→1.21%</t>
         </is>
       </c>
       <c r="E87" s="13" t="inlineStr">
@@ -3614,11 +3614,11 @@
         <v>-15</v>
       </c>
       <c r="I87" s="15" t="n">
-        <v>-52320000</v>
+        <v>-59808037</v>
       </c>
       <c r="J87" s="16" t="inlineStr">
         <is>
-          <t>1.37%→1.14%</t>
+          <t>1.51%→1.25%</t>
         </is>
       </c>
       <c r="K87" s="13" t="inlineStr">
@@ -3637,11 +3637,11 @@
         <v>7</v>
       </c>
       <c r="C88" s="11" t="n">
-        <v>47129600</v>
+        <v>49772831</v>
       </c>
       <c r="D88" s="12" t="inlineStr">
         <is>
-          <t>2.26%→2.45%</t>
+          <t>2.30%→2.50%</t>
         </is>
       </c>
       <c r="E88" s="13" t="inlineStr">
@@ -3658,11 +3658,11 @@
         <v>-8</v>
       </c>
       <c r="I88" s="15" t="n">
-        <v>-52838400</v>
+        <v>-55859235</v>
       </c>
       <c r="J88" s="16" t="inlineStr">
         <is>
-          <t>1.44%→1.20%</t>
+          <t>1.47%→1.23%</t>
         </is>
       </c>
       <c r="K88" s="13" t="inlineStr">
@@ -3681,11 +3681,11 @@
         <v>6</v>
       </c>
       <c r="C89" s="11" t="n">
-        <v>34329600</v>
+        <v>36019223</v>
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
-          <t>1.80%→1.94%</t>
+          <t>1.82%→1.96%</t>
         </is>
       </c>
       <c r="E89" s="13" t="inlineStr">
@@ -3717,796 +3717,1890 @@
       <c r="K91" s="19" t="n"/>
     </row>
     <row r="93" ht="19" customHeight="1">
-      <c r="A93" s="18" t="inlineStr">
-        <is>
-          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B93" s="19" t="n"/>
-      <c r="C93" s="19" t="n"/>
-      <c r="D93" s="19" t="n"/>
-      <c r="E93" s="19" t="n"/>
-      <c r="F93" s="19" t="n"/>
-      <c r="G93" s="19" t="n"/>
-      <c r="H93" s="19" t="n"/>
-      <c r="I93" s="19" t="n"/>
-      <c r="J93" s="19" t="n"/>
-      <c r="K93" s="19" t="n"/>
-    </row>
-    <row r="95" ht="19" customHeight="1">
-      <c r="A95" s="3" t="inlineStr">
-        <is>
-          <t>■ DS 코스닥액티브  (DS)      순자산 ≈ 799억   ·   현금 2억(0.2%)      오늘 2026-10-28  vs  5일전 2026-10-21      매수 13종목  /  매도 15종목</t>
-        </is>
-      </c>
-      <c r="B95" s="4" t="n"/>
-      <c r="C95" s="4" t="n"/>
-      <c r="D95" s="4" t="n"/>
-      <c r="E95" s="4" t="n"/>
-      <c r="F95" s="4" t="n"/>
-      <c r="G95" s="4" t="n"/>
-      <c r="H95" s="4" t="n"/>
-      <c r="I95" s="4" t="n"/>
-      <c r="J95" s="4" t="n"/>
-      <c r="K95" s="4" t="n"/>
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,014억   ·   현금 69억(6.9%)      오늘 2026-10-28  vs  5일전 2026-10-21      매수 1종목  /  매도 3종목</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="n"/>
+      <c r="C93" s="4" t="n"/>
+      <c r="D93" s="4" t="n"/>
+      <c r="E93" s="4" t="n"/>
+      <c r="F93" s="4" t="n"/>
+      <c r="G93" s="4" t="n"/>
+      <c r="H93" s="4" t="n"/>
+      <c r="I93" s="4" t="n"/>
+      <c r="J93" s="4" t="n"/>
+      <c r="K93" s="4" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="n"/>
+      <c r="C94" s="6" t="n"/>
+      <c r="D94" s="6" t="n"/>
+      <c r="E94" s="6" t="n"/>
+      <c r="G94" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H94" s="8" t="n"/>
+      <c r="I94" s="8" t="n"/>
+      <c r="J94" s="8" t="n"/>
+      <c r="K94" s="8" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B95" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C95" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D95" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E95" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G95" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H95" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I95" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J95" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K95" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
     </row>
     <row r="96">
-      <c r="A96" s="5" t="inlineStr">
+      <c r="A96" s="10" t="inlineStr">
+        <is>
+          <t>프로티나</t>
+        </is>
+      </c>
+      <c r="B96" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C96" s="11" t="n">
+        <v>508101465</v>
+      </c>
+      <c r="D96" s="12" t="inlineStr">
+        <is>
+          <t>3.35%→3.01%</t>
+        </is>
+      </c>
+      <c r="E96" s="13" t="inlineStr">
+        <is>
+          <t>23→28</t>
+        </is>
+      </c>
+      <c r="G96" s="14" t="inlineStr">
+        <is>
+          <t>유한양행</t>
+        </is>
+      </c>
+      <c r="H96" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I96" s="15" t="n">
+        <v>-830400760</v>
+      </c>
+      <c r="J96" s="16" t="inlineStr">
+        <is>
+          <t>0.00%→1.23%</t>
+        </is>
+      </c>
+      <c r="K96" s="13" t="inlineStr">
+        <is>
+          <t>12→7</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="17" t="n"/>
+      <c r="B97" s="17" t="n"/>
+      <c r="C97" s="17" t="n"/>
+      <c r="D97" s="17" t="n"/>
+      <c r="E97" s="17" t="n"/>
+      <c r="G97" s="14" t="inlineStr">
+        <is>
+          <t>리가켐바이오</t>
+        </is>
+      </c>
+      <c r="H97" s="15" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I97" s="15" t="n">
+        <v>-530626086</v>
+      </c>
+      <c r="J97" s="16" t="inlineStr">
+        <is>
+          <t>7.61%→5.06%</t>
+        </is>
+      </c>
+      <c r="K97" s="13" t="inlineStr">
+        <is>
+          <t>40→36</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="17" t="n"/>
+      <c r="B98" s="17" t="n"/>
+      <c r="C98" s="17" t="n"/>
+      <c r="D98" s="17" t="n"/>
+      <c r="E98" s="17" t="n"/>
+      <c r="G98" s="14" t="inlineStr">
+        <is>
+          <t>와이바이오로직스</t>
+        </is>
+      </c>
+      <c r="H98" s="15" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I98" s="15" t="n">
+        <v>-84700878</v>
+      </c>
+      <c r="J98" s="16" t="inlineStr">
+        <is>
+          <t>0.46%→0.25%</t>
+        </is>
+      </c>
+      <c r="K98" s="13" t="inlineStr">
+        <is>
+          <t>15→11</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="19" customHeight="1">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>■ DS 코스닥액티브  (DS)      순자산 ≈ 855억      오늘 2026-10-28  vs  5일전 2026-10-21      매수 13종목  /  매도 15종목</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="n"/>
+      <c r="C100" s="4" t="n"/>
+      <c r="D100" s="4" t="n"/>
+      <c r="E100" s="4" t="n"/>
+      <c r="F100" s="4" t="n"/>
+      <c r="G100" s="4" t="n"/>
+      <c r="H100" s="4" t="n"/>
+      <c r="I100" s="4" t="n"/>
+      <c r="J100" s="4" t="n"/>
+      <c r="K100" s="4" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B96" s="6" t="n"/>
-      <c r="C96" s="6" t="n"/>
-      <c r="D96" s="6" t="n"/>
-      <c r="E96" s="6" t="n"/>
-      <c r="G96" s="7" t="inlineStr">
+      <c r="B101" s="6" t="n"/>
+      <c r="C101" s="6" t="n"/>
+      <c r="D101" s="6" t="n"/>
+      <c r="E101" s="6" t="n"/>
+      <c r="G101" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H96" s="8" t="n"/>
-      <c r="I96" s="8" t="n"/>
-      <c r="J96" s="8" t="n"/>
-      <c r="K96" s="8" t="n"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="9" t="inlineStr">
+      <c r="H101" s="8" t="n"/>
+      <c r="I101" s="8" t="n"/>
+      <c r="J101" s="8" t="n"/>
+      <c r="K101" s="8" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B97" s="9" t="inlineStr">
+      <c r="B102" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C97" s="9" t="inlineStr">
+      <c r="C102" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D97" s="9" t="inlineStr">
+      <c r="D102" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E97" s="9" t="inlineStr">
+      <c r="E102" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G97" s="9" t="inlineStr">
+      <c r="G102" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H97" s="9" t="inlineStr">
+      <c r="H102" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I97" s="9" t="inlineStr">
+      <c r="I102" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J97" s="9" t="inlineStr">
+      <c r="J102" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K97" s="9" t="inlineStr">
+      <c r="K102" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="10" t="inlineStr">
-        <is>
-          <t>뉴파워프라즈마</t>
-        </is>
-      </c>
-      <c r="B98" s="11" t="n">
-        <v>612</v>
-      </c>
-      <c r="C98" s="11" t="n">
-        <v>1499057994</v>
-      </c>
-      <c r="D98" s="12" t="inlineStr">
-        <is>
-          <t>2.06%→4.14%</t>
-        </is>
-      </c>
-      <c r="E98" s="13" t="inlineStr">
-        <is>
-          <t>815→1,427</t>
-        </is>
-      </c>
-      <c r="G98" s="14" t="inlineStr">
-        <is>
-          <t>엠케이전자</t>
-        </is>
-      </c>
-      <c r="H98" s="15" t="n">
-        <v>-597</v>
-      </c>
-      <c r="I98" s="15" t="n">
-        <v>-1361017368</v>
-      </c>
-      <c r="J98" s="16" t="inlineStr">
-        <is>
-          <t>3.41%→1.46%</t>
-        </is>
-      </c>
-      <c r="K98" s="13" t="inlineStr">
-        <is>
-          <t>1,137→540</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="10" t="inlineStr">
-        <is>
-          <t>아스플로</t>
-        </is>
-      </c>
-      <c r="B99" s="11" t="n">
-        <v>237</v>
-      </c>
-      <c r="C99" s="11" t="n">
-        <v>1152673749</v>
-      </c>
-      <c r="D99" s="12" t="inlineStr">
-        <is>
-          <t>2.17%→3.61%</t>
-        </is>
-      </c>
-      <c r="E99" s="13" t="inlineStr">
-        <is>
-          <t>389→626</t>
-        </is>
-      </c>
-      <c r="G99" s="14" t="inlineStr">
-        <is>
-          <t>SFA  (편출)</t>
-        </is>
-      </c>
-      <c r="H99" s="15" t="n">
-        <v>-320</v>
-      </c>
-      <c r="I99" s="15" t="n">
-        <v>-1462272696</v>
-      </c>
-      <c r="J99" s="16" t="inlineStr">
-        <is>
-          <t>1.72%→0.00%</t>
-        </is>
-      </c>
-      <c r="K99" s="13" t="inlineStr">
-        <is>
-          <t>320→0</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="10" t="inlineStr">
-        <is>
-          <t>에프에스티</t>
-        </is>
-      </c>
-      <c r="B100" s="11" t="n">
-        <v>225</v>
-      </c>
-      <c r="C100" s="11" t="n">
-        <v>980910467</v>
-      </c>
-      <c r="D100" s="12" t="inlineStr">
-        <is>
-          <t>0.99%→2.11%</t>
-        </is>
-      </c>
-      <c r="E100" s="13" t="inlineStr">
-        <is>
-          <t>183→408</t>
-        </is>
-      </c>
-      <c r="G100" s="14" t="inlineStr">
-        <is>
-          <t>코세스</t>
-        </is>
-      </c>
-      <c r="H100" s="15" t="n">
-        <v>-319</v>
-      </c>
-      <c r="I100" s="15" t="n">
-        <v>-1942710925</v>
-      </c>
-      <c r="J100" s="16" t="inlineStr">
-        <is>
-          <t>3.59%→1.78%</t>
-        </is>
-      </c>
-      <c r="K100" s="13" t="inlineStr">
-        <is>
-          <t>565→246</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="10" t="inlineStr">
-        <is>
-          <t>RFHIC  (신규)</t>
-        </is>
-      </c>
-      <c r="B101" s="11" t="n">
-        <v>209</v>
-      </c>
-      <c r="C101" s="11" t="n">
-        <v>1646753584</v>
-      </c>
-      <c r="D101" s="12" t="inlineStr">
-        <is>
-          <t>0.00%→1.95%</t>
-        </is>
-      </c>
-      <c r="E101" s="13" t="inlineStr">
-        <is>
-          <t>0→209</t>
-        </is>
-      </c>
-      <c r="G101" s="14" t="inlineStr">
-        <is>
-          <t>디케이티</t>
-        </is>
-      </c>
-      <c r="H101" s="15" t="n">
-        <v>-189</v>
-      </c>
-      <c r="I101" s="15" t="n">
-        <v>-812851587</v>
-      </c>
-      <c r="J101" s="16" t="inlineStr">
-        <is>
-          <t>5.01%→4.93%</t>
-        </is>
-      </c>
-      <c r="K101" s="13" t="inlineStr">
-        <is>
-          <t>1,155→966</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="10" t="inlineStr">
-        <is>
-          <t>샘씨엔에스</t>
-        </is>
-      </c>
-      <c r="B102" s="11" t="n">
-        <v>193</v>
-      </c>
-      <c r="C102" s="11" t="n">
-        <v>517487286</v>
-      </c>
-      <c r="D102" s="12" t="inlineStr">
-        <is>
-          <t>5.31%→5.99%</t>
-        </is>
-      </c>
-      <c r="E102" s="13" t="inlineStr">
-        <is>
-          <t>1,690→1,883</t>
-        </is>
-      </c>
-      <c r="G102" s="14" t="inlineStr">
-        <is>
-          <t>태웅  (편출)</t>
-        </is>
-      </c>
-      <c r="H102" s="15" t="n">
-        <v>-186</v>
-      </c>
-      <c r="I102" s="15" t="n">
-        <v>-854633207</v>
-      </c>
-      <c r="J102" s="16" t="inlineStr">
-        <is>
-          <t>1.00%→0.00%</t>
-        </is>
-      </c>
-      <c r="K102" s="13" t="inlineStr">
-        <is>
-          <t>186→0</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>에스티아이</t>
+          <t>뉴파워프라즈마</t>
         </is>
       </c>
       <c r="B103" s="11" t="n">
-        <v>168</v>
+        <v>612</v>
       </c>
       <c r="C103" s="11" t="n">
-        <v>715478741</v>
+        <v>1516903557</v>
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>1.97%→2.69%</t>
+          <t>2.06%→4.14%</t>
         </is>
       </c>
       <c r="E103" s="13" t="inlineStr">
         <is>
-          <t>365→533</t>
+          <t>815→1,427</t>
         </is>
       </c>
       <c r="G103" s="14" t="inlineStr">
         <is>
-          <t>저스템</t>
+          <t>엠케이전자</t>
         </is>
       </c>
       <c r="H103" s="15" t="n">
-        <v>-152</v>
+        <v>-597</v>
       </c>
       <c r="I103" s="15" t="n">
-        <v>-342948643</v>
+        <v>-1377219624</v>
       </c>
       <c r="J103" s="16" t="inlineStr">
         <is>
-          <t>2.34%→1.89%</t>
+          <t>3.41%→1.46%</t>
         </is>
       </c>
       <c r="K103" s="13" t="inlineStr">
         <is>
-          <t>857→705</t>
+          <t>1,137→540</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="10" t="inlineStr">
         <is>
-          <t>동진쎄미켐</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="B104" s="11" t="n">
-        <v>95</v>
+        <v>237</v>
       </c>
       <c r="C104" s="11" t="n">
-        <v>616854294</v>
+        <v>1166395774</v>
       </c>
       <c r="D104" s="12" t="inlineStr">
         <is>
-          <t>2.18%→2.85%</t>
+          <t>2.17%→3.61%</t>
         </is>
       </c>
       <c r="E104" s="13" t="inlineStr">
         <is>
-          <t>275→370</t>
+          <t>389→626</t>
         </is>
       </c>
       <c r="G104" s="14" t="inlineStr">
         <is>
-          <t>네오셈</t>
+          <t>SFA  (편출)</t>
         </is>
       </c>
       <c r="H104" s="15" t="n">
-        <v>-108</v>
+        <v>-320</v>
       </c>
       <c r="I104" s="15" t="n">
-        <v>-310806868</v>
+        <v>-1479680348</v>
       </c>
       <c r="J104" s="16" t="inlineStr">
         <is>
-          <t>2.41%→2.35%</t>
+          <t>1.72%→0.00%</t>
         </is>
       </c>
       <c r="K104" s="13" t="inlineStr">
         <is>
-          <t>797→689</t>
+          <t>320→0</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="B105" s="11" t="n">
-        <v>86</v>
+        <v>225</v>
       </c>
       <c r="C105" s="11" t="n">
-        <v>337360961</v>
+        <v>992587734</v>
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
-          <t>1.44%→1.86%</t>
+          <t>0.99%→2.11%</t>
         </is>
       </c>
       <c r="E105" s="13" t="inlineStr">
         <is>
-          <t>313→399</t>
+          <t>183→408</t>
         </is>
       </c>
       <c r="G105" s="14" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="H105" s="15" t="n">
-        <v>-61</v>
+        <v>-319</v>
       </c>
       <c r="I105" s="15" t="n">
-        <v>-629227500</v>
+        <v>-1965837963</v>
       </c>
       <c r="J105" s="16" t="inlineStr">
         <is>
-          <t>4.72%→3.58%</t>
+          <t>3.59%→1.78%</t>
         </is>
       </c>
       <c r="K105" s="13" t="inlineStr">
         <is>
-          <t>354→293</t>
+          <t>565→246</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="10" t="inlineStr">
         <is>
-          <t>미코</t>
+          <t>RFHIC  (신규)</t>
         </is>
       </c>
       <c r="B106" s="11" t="n">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="C106" s="11" t="n">
-        <v>287632937</v>
+        <v>1666357392</v>
       </c>
       <c r="D106" s="12" t="inlineStr">
         <is>
-          <t>4.70%→5.61%</t>
+          <t>0.00%→1.95%</t>
         </is>
       </c>
       <c r="E106" s="13" t="inlineStr">
         <is>
-          <t>1,206→1,284</t>
+          <t>0→209</t>
         </is>
       </c>
       <c r="G106" s="14" t="inlineStr">
         <is>
-          <t>프로텍</t>
+          <t>디케이티</t>
         </is>
       </c>
       <c r="H106" s="15" t="n">
-        <v>-41</v>
+        <v>-189</v>
       </c>
       <c r="I106" s="15" t="n">
-        <v>-418790599</v>
+        <v>-822528194</v>
       </c>
       <c r="J106" s="16" t="inlineStr">
         <is>
-          <t>0.92%→0.40%</t>
+          <t>5.01%→4.93%</t>
         </is>
       </c>
       <c r="K106" s="13" t="inlineStr">
         <is>
-          <t>74→33</t>
+          <t>1,155→966</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>샘씨엔에스</t>
         </is>
       </c>
       <c r="B107" s="11" t="n">
-        <v>51</v>
+        <v>193</v>
       </c>
       <c r="C107" s="11" t="n">
-        <v>494373835</v>
+        <v>523647723</v>
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>2.40%→3.07%</t>
+          <t>5.31%→5.99%</t>
         </is>
       </c>
       <c r="E107" s="13" t="inlineStr">
         <is>
-          <t>216→267</t>
+          <t>1,690→1,883</t>
         </is>
       </c>
       <c r="G107" s="14" t="inlineStr">
         <is>
-          <t>제주반도체</t>
+          <t>태웅  (편출)</t>
         </is>
       </c>
       <c r="H107" s="15" t="n">
-        <v>-15</v>
+        <v>-186</v>
       </c>
       <c r="I107" s="15" t="n">
-        <v>-161028077</v>
+        <v>-864807203</v>
       </c>
       <c r="J107" s="16" t="inlineStr">
         <is>
-          <t>0.69%→0.48%</t>
+          <t>1.00%→0.00%</t>
         </is>
       </c>
       <c r="K107" s="13" t="inlineStr">
         <is>
-          <t>53→38</t>
+          <t>186→0</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="10" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>에스티아이</t>
         </is>
       </c>
       <c r="B108" s="11" t="n">
-        <v>46</v>
+        <v>168</v>
       </c>
       <c r="C108" s="11" t="n">
-        <v>862445211</v>
+        <v>723996170</v>
       </c>
       <c r="D108" s="12" t="inlineStr">
         <is>
-          <t>1.05%→2.13%</t>
+          <t>1.97%→2.69%</t>
         </is>
       </c>
       <c r="E108" s="13" t="inlineStr">
         <is>
-          <t>50→96</t>
+          <t>365→533</t>
         </is>
       </c>
       <c r="G108" s="14" t="inlineStr">
         <is>
-          <t>티씨케이  (편출)</t>
+          <t>저스템</t>
         </is>
       </c>
       <c r="H108" s="15" t="n">
-        <v>-13</v>
+        <v>-152</v>
       </c>
       <c r="I108" s="15" t="n">
-        <v>-487032232</v>
+        <v>-347031282</v>
       </c>
       <c r="J108" s="16" t="inlineStr">
         <is>
-          <t>0.57%→0.00%</t>
+          <t>2.34%→1.89%</t>
         </is>
       </c>
       <c r="K108" s="13" t="inlineStr">
         <is>
-          <t>13→0</t>
+          <t>857→705</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>이엔에프테크놀로지</t>
+          <t>동진쎄미켐</t>
         </is>
       </c>
       <c r="B109" s="11" t="n">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="C109" s="11" t="n">
-        <v>226598508</v>
+        <v>624197647</v>
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>3.15%→3.43%</t>
+          <t>2.18%→2.85%</t>
         </is>
       </c>
       <c r="E109" s="13" t="inlineStr">
         <is>
-          <t>376→408</t>
+          <t>275→370</t>
         </is>
       </c>
       <c r="G109" s="14" t="inlineStr">
         <is>
-          <t>파크시스템스</t>
+          <t>네오셈</t>
         </is>
       </c>
       <c r="H109" s="15" t="n">
-        <v>-7</v>
+        <v>-108</v>
       </c>
       <c r="I109" s="15" t="n">
-        <v>-265188126</v>
+        <v>-314506874</v>
       </c>
       <c r="J109" s="16" t="inlineStr">
         <is>
-          <t>1.97%→1.48%</t>
+          <t>2.41%→2.35%</t>
         </is>
       </c>
       <c r="K109" s="13" t="inlineStr">
         <is>
-          <t>40→33</t>
+          <t>797→689</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="10" t="inlineStr">
         <is>
+          <t>코미코</t>
+        </is>
+      </c>
+      <c r="B110" s="11" t="n">
+        <v>86</v>
+      </c>
+      <c r="C110" s="11" t="n">
+        <v>341377080</v>
+      </c>
+      <c r="D110" s="12" t="inlineStr">
+        <is>
+          <t>1.44%→1.86%</t>
+        </is>
+      </c>
+      <c r="E110" s="13" t="inlineStr">
+        <is>
+          <t>313→399</t>
+        </is>
+      </c>
+      <c r="G110" s="14" t="inlineStr">
+        <is>
+          <t>리노공업</t>
+        </is>
+      </c>
+      <c r="H110" s="15" t="n">
+        <v>-61</v>
+      </c>
+      <c r="I110" s="15" t="n">
+        <v>-636718150</v>
+      </c>
+      <c r="J110" s="16" t="inlineStr">
+        <is>
+          <t>4.72%→3.58%</t>
+        </is>
+      </c>
+      <c r="K110" s="13" t="inlineStr">
+        <is>
+          <t>354→293</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="10" t="inlineStr">
+        <is>
+          <t>미코</t>
+        </is>
+      </c>
+      <c r="B111" s="11" t="n">
+        <v>78</v>
+      </c>
+      <c r="C111" s="11" t="n">
+        <v>291057068</v>
+      </c>
+      <c r="D111" s="12" t="inlineStr">
+        <is>
+          <t>4.70%→5.61%</t>
+        </is>
+      </c>
+      <c r="E111" s="13" t="inlineStr">
+        <is>
+          <t>1,206→1,284</t>
+        </is>
+      </c>
+      <c r="G111" s="14" t="inlineStr">
+        <is>
+          <t>프로텍</t>
+        </is>
+      </c>
+      <c r="H111" s="15" t="n">
+        <v>-41</v>
+      </c>
+      <c r="I111" s="15" t="n">
+        <v>-423776100</v>
+      </c>
+      <c r="J111" s="16" t="inlineStr">
+        <is>
+          <t>0.92%→0.40%</t>
+        </is>
+      </c>
+      <c r="K111" s="13" t="inlineStr">
+        <is>
+          <t>74→33</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="10" t="inlineStr">
+        <is>
+          <t>인텍플러스</t>
+        </is>
+      </c>
+      <c r="B112" s="11" t="n">
+        <v>51</v>
+      </c>
+      <c r="C112" s="11" t="n">
+        <v>500259118</v>
+      </c>
+      <c r="D112" s="12" t="inlineStr">
+        <is>
+          <t>2.40%→3.07%</t>
+        </is>
+      </c>
+      <c r="E112" s="13" t="inlineStr">
+        <is>
+          <t>216→267</t>
+        </is>
+      </c>
+      <c r="G112" s="14" t="inlineStr">
+        <is>
+          <t>제주반도체</t>
+        </is>
+      </c>
+      <c r="H112" s="15" t="n">
+        <v>-15</v>
+      </c>
+      <c r="I112" s="15" t="n">
+        <v>-162945038</v>
+      </c>
+      <c r="J112" s="16" t="inlineStr">
+        <is>
+          <t>0.69%→0.48%</t>
+        </is>
+      </c>
+      <c r="K112" s="13" t="inlineStr">
+        <is>
+          <t>53→38</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="10" t="inlineStr">
+        <is>
+          <t>기가비스</t>
+        </is>
+      </c>
+      <c r="B113" s="11" t="n">
+        <v>46</v>
+      </c>
+      <c r="C113" s="11" t="n">
+        <v>872712205</v>
+      </c>
+      <c r="D113" s="12" t="inlineStr">
+        <is>
+          <t>1.05%→2.13%</t>
+        </is>
+      </c>
+      <c r="E113" s="13" t="inlineStr">
+        <is>
+          <t>50→96</t>
+        </is>
+      </c>
+      <c r="G113" s="14" t="inlineStr">
+        <is>
+          <t>티씨케이  (편출)</t>
+        </is>
+      </c>
+      <c r="H113" s="15" t="n">
+        <v>-13</v>
+      </c>
+      <c r="I113" s="15" t="n">
+        <v>-492830116</v>
+      </c>
+      <c r="J113" s="16" t="inlineStr">
+        <is>
+          <t>0.57%→0.00%</t>
+        </is>
+      </c>
+      <c r="K113" s="13" t="inlineStr">
+        <is>
+          <t>13→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="10" t="inlineStr">
+        <is>
+          <t>이엔에프테크놀로지</t>
+        </is>
+      </c>
+      <c r="B114" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="C114" s="11" t="n">
+        <v>229296054</v>
+      </c>
+      <c r="D114" s="12" t="inlineStr">
+        <is>
+          <t>3.15%→3.43%</t>
+        </is>
+      </c>
+      <c r="E114" s="13" t="inlineStr">
+        <is>
+          <t>376→408</t>
+        </is>
+      </c>
+      <c r="G114" s="14" t="inlineStr">
+        <is>
+          <t>파크시스템스</t>
+        </is>
+      </c>
+      <c r="H114" s="15" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I114" s="15" t="n">
+        <v>-268345063</v>
+      </c>
+      <c r="J114" s="16" t="inlineStr">
+        <is>
+          <t>1.97%→1.48%</t>
+        </is>
+      </c>
+      <c r="K114" s="13" t="inlineStr">
+        <is>
+          <t>40→33</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="10" t="inlineStr">
+        <is>
           <t>솔브레인</t>
         </is>
       </c>
-      <c r="B110" s="11" t="n">
+      <c r="B115" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C110" s="11" t="n">
-        <v>309456147</v>
-      </c>
-      <c r="D110" s="12" t="inlineStr">
+      <c r="C115" s="11" t="n">
+        <v>313140074</v>
+      </c>
+      <c r="D115" s="12" t="inlineStr">
         <is>
           <t>2.81%→3.12%</t>
         </is>
       </c>
-      <c r="E110" s="13" t="inlineStr">
+      <c r="E115" s="13" t="inlineStr">
         <is>
           <t>45→51</t>
         </is>
       </c>
-      <c r="G110" s="14" t="inlineStr">
+      <c r="G115" s="14" t="inlineStr">
         <is>
           <t>피에스케이홀딩스</t>
         </is>
       </c>
-      <c r="H110" s="15" t="n">
+      <c r="H115" s="15" t="n">
         <v>-5</v>
       </c>
-      <c r="I110" s="15" t="n">
-        <v>-142128068</v>
-      </c>
-      <c r="J110" s="16" t="inlineStr">
+      <c r="I115" s="15" t="n">
+        <v>-143820034</v>
+      </c>
+      <c r="J115" s="16" t="inlineStr">
         <is>
           <t>2.44%→2.16%</t>
         </is>
       </c>
-      <c r="K110" s="13" t="inlineStr">
+      <c r="K115" s="13" t="inlineStr">
         <is>
           <t>69→64</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="17" t="n"/>
-      <c r="B111" s="17" t="n"/>
-      <c r="C111" s="17" t="n"/>
-      <c r="D111" s="17" t="n"/>
-      <c r="E111" s="17" t="n"/>
-      <c r="G111" s="14" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="17" t="n"/>
+      <c r="B116" s="17" t="n"/>
+      <c r="C116" s="17" t="n"/>
+      <c r="D116" s="17" t="n"/>
+      <c r="E116" s="17" t="n"/>
+      <c r="G116" s="14" t="inlineStr">
+        <is>
+          <t>이오테크닉스</t>
+        </is>
+      </c>
+      <c r="H116" s="15" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I116" s="15" t="n">
+        <v>-268600063</v>
+      </c>
+      <c r="J116" s="16" t="inlineStr">
+        <is>
+          <t>4.40%→3.86%</t>
+        </is>
+      </c>
+      <c r="K116" s="13" t="inlineStr">
+        <is>
+          <t>53→49</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="17" t="n"/>
+      <c r="B117" s="17" t="n"/>
+      <c r="C117" s="17" t="n"/>
+      <c r="D117" s="17" t="n"/>
+      <c r="E117" s="17" t="n"/>
+      <c r="G117" s="14" t="inlineStr">
         <is>
           <t>티에스이</t>
         </is>
       </c>
-      <c r="H111" s="15" t="n">
+      <c r="H117" s="15" t="n">
         <v>-4</v>
       </c>
-      <c r="I111" s="15" t="n">
-        <v>-174720083</v>
-      </c>
-      <c r="J111" s="16" t="inlineStr">
+      <c r="I117" s="15" t="n">
+        <v>-176800042</v>
+      </c>
+      <c r="J117" s="16" t="inlineStr">
         <is>
           <t>2.39%→2.18%</t>
         </is>
       </c>
-      <c r="K111" s="13" t="inlineStr">
+      <c r="K117" s="13" t="inlineStr">
         <is>
           <t>46→42</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="17" t="n"/>
-      <c r="B112" s="17" t="n"/>
-      <c r="C112" s="17" t="n"/>
-      <c r="D112" s="17" t="n"/>
-      <c r="E112" s="17" t="n"/>
-      <c r="G112" s="14" t="inlineStr">
+    <row r="119" ht="19" customHeight="1">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>■ TIGER 코스닥액티브  (미래에셋)      순자산 ≈ 292억   ·   현금 3억(1.1%)      오늘 2026-10-28  vs  5일전 2026-10-21      매수 12종목  /  매도 15종목</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="n"/>
+      <c r="C119" s="4" t="n"/>
+      <c r="D119" s="4" t="n"/>
+      <c r="E119" s="4" t="n"/>
+      <c r="F119" s="4" t="n"/>
+      <c r="G119" s="4" t="n"/>
+      <c r="H119" s="4" t="n"/>
+      <c r="I119" s="4" t="n"/>
+      <c r="J119" s="4" t="n"/>
+      <c r="K119" s="4" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B120" s="6" t="n"/>
+      <c r="C120" s="6" t="n"/>
+      <c r="D120" s="6" t="n"/>
+      <c r="E120" s="6" t="n"/>
+      <c r="G120" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H120" s="8" t="n"/>
+      <c r="I120" s="8" t="n"/>
+      <c r="J120" s="8" t="n"/>
+      <c r="K120" s="8" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B121" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C121" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D121" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E121" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G121" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H121" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I121" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J121" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K121" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="10" t="inlineStr">
+        <is>
+          <t>파인엠텍  (신규)</t>
+        </is>
+      </c>
+      <c r="B122" s="11" t="n">
+        <v>61</v>
+      </c>
+      <c r="C122" s="11" t="n">
+        <v>254242081</v>
+      </c>
+      <c r="D122" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.88%</t>
+        </is>
+      </c>
+      <c r="E122" s="13" t="inlineStr">
+        <is>
+          <t>0→61</t>
+        </is>
+      </c>
+      <c r="G122" s="14" t="inlineStr">
+        <is>
+          <t>동국산업</t>
+        </is>
+      </c>
+      <c r="H122" s="15" t="n">
+        <v>-135</v>
+      </c>
+      <c r="I122" s="15" t="n">
+        <v>-214836453</v>
+      </c>
+      <c r="J122" s="16" t="inlineStr">
+        <is>
+          <t>1.69%→0.94%</t>
+        </is>
+      </c>
+      <c r="K122" s="13" t="inlineStr">
+        <is>
+          <t>305→170</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="10" t="inlineStr">
+        <is>
+          <t>루닛  (신규)</t>
+        </is>
+      </c>
+      <c r="B123" s="11" t="n">
+        <v>61</v>
+      </c>
+      <c r="C123" s="11" t="n">
+        <v>376226918</v>
+      </c>
+      <c r="D123" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.30%</t>
+        </is>
+      </c>
+      <c r="E123" s="13" t="inlineStr">
+        <is>
+          <t>0→61</t>
+        </is>
+      </c>
+      <c r="G123" s="14" t="inlineStr">
+        <is>
+          <t>피노</t>
+        </is>
+      </c>
+      <c r="H123" s="15" t="n">
+        <v>-120</v>
+      </c>
+      <c r="I123" s="15" t="n">
+        <v>-366270261</v>
+      </c>
+      <c r="J123" s="16" t="inlineStr">
+        <is>
+          <t>3.30%→2.02%</t>
+        </is>
+      </c>
+      <c r="K123" s="13" t="inlineStr">
+        <is>
+          <t>311→191</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="10" t="inlineStr">
+        <is>
+          <t>지투지바이오</t>
+        </is>
+      </c>
+      <c r="B124" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="C124" s="11" t="n">
+        <v>230750264</v>
+      </c>
+      <c r="D124" s="12" t="inlineStr">
+        <is>
+          <t>0.52%→1.31%</t>
+        </is>
+      </c>
+      <c r="E124" s="13" t="inlineStr">
+        <is>
+          <t>9→23</t>
+        </is>
+      </c>
+      <c r="G124" s="14" t="inlineStr">
+        <is>
+          <t>피엠티</t>
+        </is>
+      </c>
+      <c r="H124" s="15" t="n">
+        <v>-50</v>
+      </c>
+      <c r="I124" s="15" t="n">
+        <v>-69149299</v>
+      </c>
+      <c r="J124" s="16" t="inlineStr">
+        <is>
+          <t>0.26%→0.01%</t>
+        </is>
+      </c>
+      <c r="K124" s="13" t="inlineStr">
+        <is>
+          <t>53→3</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="10" t="inlineStr">
+        <is>
+          <t>인텍플러스</t>
+        </is>
+      </c>
+      <c r="B125" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="C125" s="11" t="n">
+        <v>267208890</v>
+      </c>
+      <c r="D125" s="12" t="inlineStr">
+        <is>
+          <t>2.20%→3.12%</t>
+        </is>
+      </c>
+      <c r="E125" s="13" t="inlineStr">
+        <is>
+          <t>26→37</t>
+        </is>
+      </c>
+      <c r="G125" s="14" t="inlineStr">
+        <is>
+          <t>HLB이노베이션  (편출)</t>
+        </is>
+      </c>
+      <c r="H125" s="15" t="n">
+        <v>-40</v>
+      </c>
+      <c r="I125" s="15" t="n">
+        <v>-247548176</v>
+      </c>
+      <c r="J125" s="16" t="inlineStr">
+        <is>
+          <t>0.86%→0.00%</t>
+        </is>
+      </c>
+      <c r="K125" s="13" t="inlineStr">
+        <is>
+          <t>40→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="10" t="inlineStr">
+        <is>
+          <t>프로티나</t>
+        </is>
+      </c>
+      <c r="B126" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="C126" s="11" t="n">
+        <v>226687612</v>
+      </c>
+      <c r="D126" s="12" t="inlineStr">
+        <is>
+          <t>1.29%→2.07%</t>
+        </is>
+      </c>
+      <c r="E126" s="13" t="inlineStr">
+        <is>
+          <t>18→29</t>
+        </is>
+      </c>
+      <c r="G126" s="14" t="inlineStr">
+        <is>
+          <t>서진시스템</t>
+        </is>
+      </c>
+      <c r="H126" s="15" t="n">
+        <v>-37</v>
+      </c>
+      <c r="I126" s="15" t="n">
+        <v>-467310333</v>
+      </c>
+      <c r="J126" s="16" t="inlineStr">
+        <is>
+          <t>4.44%→2.80%</t>
+        </is>
+      </c>
+      <c r="K126" s="13" t="inlineStr">
+        <is>
+          <t>101→64</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="10" t="inlineStr">
+        <is>
+          <t>선익시스템  (신규)</t>
+        </is>
+      </c>
+      <c r="B127" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C127" s="11" t="n">
+        <v>319034027</v>
+      </c>
+      <c r="D127" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.11%</t>
+        </is>
+      </c>
+      <c r="E127" s="13" t="inlineStr">
+        <is>
+          <t>0→9</t>
+        </is>
+      </c>
+      <c r="G127" s="14" t="inlineStr">
+        <is>
+          <t>에이팩트</t>
+        </is>
+      </c>
+      <c r="H127" s="15" t="n">
+        <v>-24</v>
+      </c>
+      <c r="I127" s="15" t="n">
+        <v>-101545272</v>
+      </c>
+      <c r="J127" s="16" t="inlineStr">
+        <is>
+          <t>3.53%→3.17%</t>
+        </is>
+      </c>
+      <c r="K127" s="13" t="inlineStr">
+        <is>
+          <t>240→216</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="10" t="inlineStr">
+        <is>
+          <t>알지노믹스</t>
+        </is>
+      </c>
+      <c r="B128" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C128" s="11" t="n">
+        <v>85442011</v>
+      </c>
+      <c r="D128" s="12" t="inlineStr">
+        <is>
+          <t>0.69%→0.99%</t>
+        </is>
+      </c>
+      <c r="E128" s="13" t="inlineStr">
+        <is>
+          <t>21→30</t>
+        </is>
+      </c>
+      <c r="G128" s="14" t="inlineStr">
+        <is>
+          <t>덕산하이메탈</t>
+        </is>
+      </c>
+      <c r="H128" s="15" t="n">
+        <v>-23</v>
+      </c>
+      <c r="I128" s="15" t="n">
+        <v>-101187422</v>
+      </c>
+      <c r="J128" s="16" t="inlineStr">
+        <is>
+          <t>0.96%→0.61%</t>
+        </is>
+      </c>
+      <c r="K128" s="13" t="inlineStr">
+        <is>
+          <t>63→40</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="10" t="inlineStr">
+        <is>
+          <t>한양디지텍</t>
+        </is>
+      </c>
+      <c r="B129" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C129" s="11" t="n">
+        <v>94598767</v>
+      </c>
+      <c r="D129" s="12" t="inlineStr">
+        <is>
+          <t>4.50%→4.81%</t>
+        </is>
+      </c>
+      <c r="E129" s="13" t="inlineStr">
+        <is>
+          <t>82→88</t>
+        </is>
+      </c>
+      <c r="G129" s="14" t="inlineStr">
+        <is>
+          <t>HT로보틱스</t>
+        </is>
+      </c>
+      <c r="H129" s="15" t="n">
+        <v>-22</v>
+      </c>
+      <c r="I129" s="15" t="n">
+        <v>-88266923</v>
+      </c>
+      <c r="J129" s="16" t="inlineStr">
+        <is>
+          <t>0.35%→0.04%</t>
+        </is>
+      </c>
+      <c r="K129" s="13" t="inlineStr">
+        <is>
+          <t>25→3</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="10" t="inlineStr">
+        <is>
+          <t>기가비스</t>
+        </is>
+      </c>
+      <c r="B130" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C130" s="11" t="n">
+        <v>187934534</v>
+      </c>
+      <c r="D130" s="12" t="inlineStr">
+        <is>
+          <t>0.49%→1.14%</t>
+        </is>
+      </c>
+      <c r="E130" s="13" t="inlineStr">
+        <is>
+          <t>3→7</t>
+        </is>
+      </c>
+      <c r="G130" s="14" t="inlineStr">
+        <is>
+          <t>한선엔지니어링</t>
+        </is>
+      </c>
+      <c r="H130" s="15" t="n">
+        <v>-18</v>
+      </c>
+      <c r="I130" s="15" t="n">
+        <v>-99271871</v>
+      </c>
+      <c r="J130" s="16" t="inlineStr">
+        <is>
+          <t>2.25%→1.89%</t>
+        </is>
+      </c>
+      <c r="K130" s="13" t="inlineStr">
+        <is>
+          <t>117→99</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="10" t="inlineStr">
+        <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="B131" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C131" s="11" t="n">
+        <v>148023705</v>
+      </c>
+      <c r="D131" s="12" t="inlineStr">
+        <is>
+          <t>5.84%→6.33%</t>
+        </is>
+      </c>
+      <c r="E131" s="13" t="inlineStr">
+        <is>
+          <t>34→37</t>
+        </is>
+      </c>
+      <c r="G131" s="14" t="inlineStr">
+        <is>
+          <t>덕산테코피아</t>
+        </is>
+      </c>
+      <c r="H131" s="15" t="n">
+        <v>-9</v>
+      </c>
+      <c r="I131" s="15" t="n">
+        <v>-37170116</v>
+      </c>
+      <c r="J131" s="16" t="inlineStr">
+        <is>
+          <t>0.33%→0.20%</t>
+        </is>
+      </c>
+      <c r="K131" s="13" t="inlineStr">
+        <is>
+          <t>23→14</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="10" t="inlineStr">
+        <is>
+          <t>올릭스</t>
+        </is>
+      </c>
+      <c r="B132" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C132" s="11" t="n">
+        <v>114427882</v>
+      </c>
+      <c r="D132" s="12" t="inlineStr">
+        <is>
+          <t>2.39%→2.78%</t>
+        </is>
+      </c>
+      <c r="E132" s="13" t="inlineStr">
+        <is>
+          <t>18→21</t>
+        </is>
+      </c>
+      <c r="G132" s="14" t="inlineStr">
+        <is>
+          <t>펌텍코리아</t>
+        </is>
+      </c>
+      <c r="H132" s="15" t="n">
+        <v>-8</v>
+      </c>
+      <c r="I132" s="15" t="n">
+        <v>-227340162</v>
+      </c>
+      <c r="J132" s="16" t="inlineStr">
+        <is>
+          <t>3.56%→2.76%</t>
+        </is>
+      </c>
+      <c r="K132" s="13" t="inlineStr">
+        <is>
+          <t>36→28</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="10" t="inlineStr">
+        <is>
+          <t>RF머트리얼즈</t>
+        </is>
+      </c>
+      <c r="B133" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C133" s="11" t="n">
+        <v>43889281</v>
+      </c>
+      <c r="D133" s="12" t="inlineStr">
+        <is>
+          <t>0.87%→1.01%</t>
+        </is>
+      </c>
+      <c r="E133" s="13" t="inlineStr">
+        <is>
+          <t>17→20</t>
+        </is>
+      </c>
+      <c r="G133" s="14" t="inlineStr">
+        <is>
+          <t>오이솔루션</t>
+        </is>
+      </c>
+      <c r="H133" s="15" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I133" s="15" t="n">
+        <v>-70875401</v>
+      </c>
+      <c r="J133" s="16" t="inlineStr">
+        <is>
+          <t>0.99%→0.74%</t>
+        </is>
+      </c>
+      <c r="K133" s="13" t="inlineStr">
+        <is>
+          <t>28→21</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="17" t="n"/>
+      <c r="B134" s="17" t="n"/>
+      <c r="C134" s="17" t="n"/>
+      <c r="D134" s="17" t="n"/>
+      <c r="E134" s="17" t="n"/>
+      <c r="G134" s="14" t="inlineStr">
+        <is>
+          <t>피에스케이</t>
+        </is>
+      </c>
+      <c r="H134" s="15" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I134" s="15" t="n">
+        <v>-290742807</v>
+      </c>
+      <c r="J134" s="16" t="inlineStr">
+        <is>
+          <t>1.69%→0.67%</t>
+        </is>
+      </c>
+      <c r="K134" s="13" t="inlineStr">
+        <is>
+          <t>10→4</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="17" t="n"/>
+      <c r="B135" s="17" t="n"/>
+      <c r="C135" s="17" t="n"/>
+      <c r="D135" s="17" t="n"/>
+      <c r="E135" s="17" t="n"/>
+      <c r="G135" s="14" t="inlineStr">
+        <is>
+          <t>인텔리안테크</t>
+        </is>
+      </c>
+      <c r="H135" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I135" s="15" t="n">
+        <v>-111354579</v>
+      </c>
+      <c r="J135" s="16" t="inlineStr">
+        <is>
+          <t>0.78%→0.39%</t>
+        </is>
+      </c>
+      <c r="K135" s="13" t="inlineStr">
+        <is>
+          <t>10→5</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="17" t="n"/>
+      <c r="B136" s="17" t="n"/>
+      <c r="C136" s="17" t="n"/>
+      <c r="D136" s="17" t="n"/>
+      <c r="E136" s="17" t="n"/>
+      <c r="G136" s="14" t="inlineStr">
+        <is>
+          <t>한라IMS</t>
+        </is>
+      </c>
+      <c r="H136" s="15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I136" s="15" t="n">
+        <v>-17555713</v>
+      </c>
+      <c r="J136" s="16" t="inlineStr">
+        <is>
+          <t>0.35%→0.28%</t>
+        </is>
+      </c>
+      <c r="K136" s="13" t="inlineStr">
+        <is>
+          <t>17→14</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="19" customHeight="1">
+      <c r="A138" s="3" t="inlineStr">
+        <is>
+          <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 55억   ·   현금 1억(1.7%)      오늘 2026-10-28  vs  5일전 2026-10-21      매수 4종목  /  매도 3종목</t>
+        </is>
+      </c>
+      <c r="B138" s="4" t="n"/>
+      <c r="C138" s="4" t="n"/>
+      <c r="D138" s="4" t="n"/>
+      <c r="E138" s="4" t="n"/>
+      <c r="F138" s="4" t="n"/>
+      <c r="G138" s="4" t="n"/>
+      <c r="H138" s="4" t="n"/>
+      <c r="I138" s="4" t="n"/>
+      <c r="J138" s="4" t="n"/>
+      <c r="K138" s="4" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B139" s="6" t="n"/>
+      <c r="C139" s="6" t="n"/>
+      <c r="D139" s="6" t="n"/>
+      <c r="E139" s="6" t="n"/>
+      <c r="G139" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H139" s="8" t="n"/>
+      <c r="I139" s="8" t="n"/>
+      <c r="J139" s="8" t="n"/>
+      <c r="K139" s="8" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B140" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C140" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D140" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E140" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G140" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H140" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I140" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J140" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K140" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="10" t="inlineStr">
+        <is>
+          <t>큐리언트  (신규)</t>
+        </is>
+      </c>
+      <c r="B141" s="11" t="n">
+        <v>176</v>
+      </c>
+      <c r="C141" s="11" t="n">
+        <v>25963520</v>
+      </c>
+      <c r="D141" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.48%</t>
+        </is>
+      </c>
+      <c r="E141" s="13" t="inlineStr">
+        <is>
+          <t>0→176</t>
+        </is>
+      </c>
+      <c r="G141" s="14" t="inlineStr">
+        <is>
+          <t>엘티씨</t>
+        </is>
+      </c>
+      <c r="H141" s="15" t="n">
+        <v>-98</v>
+      </c>
+      <c r="I141" s="15" t="n">
+        <v>-26342400</v>
+      </c>
+      <c r="J141" s="16" t="inlineStr">
+        <is>
+          <t>3.37%→2.88%</t>
+        </is>
+      </c>
+      <c r="K141" s="13" t="inlineStr">
+        <is>
+          <t>683→585</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="10" t="inlineStr">
+        <is>
+          <t>파두</t>
+        </is>
+      </c>
+      <c r="B142" s="11" t="n">
+        <v>56</v>
+      </c>
+      <c r="C142" s="11" t="n">
+        <v>21504000</v>
+      </c>
+      <c r="D142" s="12" t="inlineStr">
+        <is>
+          <t>3.17%→3.55%</t>
+        </is>
+      </c>
+      <c r="E142" s="13" t="inlineStr">
+        <is>
+          <t>449→505</t>
+        </is>
+      </c>
+      <c r="G142" s="14" t="inlineStr">
+        <is>
+          <t>테스</t>
+        </is>
+      </c>
+      <c r="H142" s="15" t="n">
+        <v>-28</v>
+      </c>
+      <c r="I142" s="15" t="n">
+        <v>-24886400</v>
+      </c>
+      <c r="J142" s="16" t="inlineStr">
+        <is>
+          <t>4.53%→4.06%</t>
+        </is>
+      </c>
+      <c r="K142" s="13" t="inlineStr">
+        <is>
+          <t>277→249</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="10" t="inlineStr">
+        <is>
+          <t>대주전자재료</t>
+        </is>
+      </c>
+      <c r="B143" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="C143" s="11" t="n">
+        <v>8947200</v>
+      </c>
+      <c r="D143" s="12" t="inlineStr">
+        <is>
+          <t>2.43%→2.58%</t>
+        </is>
+      </c>
+      <c r="E143" s="13" t="inlineStr">
+        <is>
+          <t>177→189</t>
+        </is>
+      </c>
+      <c r="G143" s="14" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="H143" s="15" t="n">
+        <v>-19</v>
+      </c>
+      <c r="I143" s="15" t="n">
+        <v>-25718400</v>
+      </c>
+      <c r="J143" s="16" t="inlineStr">
+        <is>
+          <t>5.03%→4.54%</t>
+        </is>
+      </c>
+      <c r="K143" s="13" t="inlineStr">
+        <is>
+          <t>202→183</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="10" t="inlineStr">
         <is>
           <t>이오테크닉스</t>
         </is>
       </c>
-      <c r="H112" s="15" t="n">
-        <v>-4</v>
-      </c>
-      <c r="I112" s="15" t="n">
-        <v>-265440126</v>
-      </c>
-      <c r="J112" s="16" t="inlineStr">
-        <is>
-          <t>4.40%→3.86%</t>
-        </is>
-      </c>
-      <c r="K112" s="13" t="inlineStr">
-        <is>
-          <t>53→49</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="19" customHeight="1">
-      <c r="A114" s="18" t="inlineStr">
-        <is>
-          <t>■ TIGER 코스닥액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B114" s="19" t="n"/>
-      <c r="C114" s="19" t="n"/>
-      <c r="D114" s="19" t="n"/>
-      <c r="E114" s="19" t="n"/>
-      <c r="F114" s="19" t="n"/>
-      <c r="G114" s="19" t="n"/>
-      <c r="H114" s="19" t="n"/>
-      <c r="I114" s="19" t="n"/>
-      <c r="J114" s="19" t="n"/>
-      <c r="K114" s="19" t="n"/>
-    </row>
-    <row r="116" ht="19" customHeight="1">
-      <c r="A116" s="18" t="inlineStr">
-        <is>
-          <t>■ MIDAS 코스닥액티브  (마이다스)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B116" s="19" t="n"/>
-      <c r="C116" s="19" t="n"/>
-      <c r="D116" s="19" t="n"/>
-      <c r="E116" s="19" t="n"/>
-      <c r="F116" s="19" t="n"/>
-      <c r="G116" s="19" t="n"/>
-      <c r="H116" s="19" t="n"/>
-      <c r="I116" s="19" t="n"/>
-      <c r="J116" s="19" t="n"/>
-      <c r="K116" s="19" t="n"/>
+      <c r="B144" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="C144" s="11" t="n">
+        <v>34760000</v>
+      </c>
+      <c r="D144" s="12" t="inlineStr">
+        <is>
+          <t>5.87%→6.49%</t>
+        </is>
+      </c>
+      <c r="E144" s="13" t="inlineStr">
+        <is>
+          <t>101→112</t>
+        </is>
+      </c>
+      <c r="G144" s="17" t="n"/>
+      <c r="H144" s="17" t="n"/>
+      <c r="I144" s="17" t="n"/>
+      <c r="J144" s="17" t="n"/>
+      <c r="K144" s="17" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="G96:K96"/>
-    <mergeCell ref="A114:K114"/>
+  <mergeCells count="30">
     <mergeCell ref="G72:K72"/>
     <mergeCell ref="G21:K21"/>
     <mergeCell ref="A82:E82"/>
+    <mergeCell ref="A94:E94"/>
+    <mergeCell ref="G120:K120"/>
+    <mergeCell ref="A138:K138"/>
     <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A119:K119"/>
     <mergeCell ref="G82:K82"/>
+    <mergeCell ref="G101:K101"/>
     <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A120:E120"/>
     <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A101:E101"/>
     <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A95:K95"/>
+    <mergeCell ref="A139:E139"/>
+    <mergeCell ref="G139:K139"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A71:K71"/>
-    <mergeCell ref="A116:K116"/>
     <mergeCell ref="G4:K4"/>
     <mergeCell ref="A91:K91"/>
     <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A100:K100"/>
     <mergeCell ref="A20:K20"/>
-    <mergeCell ref="A96:E96"/>
     <mergeCell ref="A72:E72"/>
     <mergeCell ref="A81:K81"/>
+    <mergeCell ref="G94:K94"/>
     <mergeCell ref="G41:K41"/>
     <mergeCell ref="A93:K93"/>
     <mergeCell ref="A40:K40"/>

--- a/reports/pdf_rolling5_20261028.xlsx
+++ b/reports/pdf_rolling5_20261028.xlsx
@@ -1054,23 +1054,23 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>파크시스템스</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>571968276</v>
+        <v>2687059299</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>0.40%→0.51%</t>
+          <t>1.43%→1.92%</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>34→46</t>
+          <t>25→37</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -1098,23 +1098,23 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>파크시스템스</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>2687059299</v>
+        <v>571968276</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>1.43%→1.92%</t>
+          <t>0.40%→0.51%</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>25→37</t>
+          <t>34→46</t>
         </is>
       </c>
       <c r="G16" s="17" t="n"/>
@@ -1684,23 +1684,23 @@
       <c r="E33" s="17" t="n"/>
       <c r="G33" s="14" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="H33" s="15" t="n">
         <v>-22</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>-949845352</v>
+        <v>-2734940287</v>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
-          <t>7.43%→6.62%</t>
+          <t>3.76%→2.56%</t>
         </is>
       </c>
       <c r="K33" s="13" t="inlineStr">
         <is>
-          <t>462→440</t>
+          <t>81→59</t>
         </is>
       </c>
     </row>
@@ -1712,23 +1712,23 @@
       <c r="E34" s="17" t="n"/>
       <c r="G34" s="14" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="H34" s="15" t="n">
         <v>-22</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-2734940287</v>
+        <v>-949845352</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
-          <t>3.76%→2.56%</t>
+          <t>7.43%→6.62%</t>
         </is>
       </c>
       <c r="K34" s="13" t="inlineStr">
         <is>
-          <t>81→59</t>
+          <t>462→440</t>
         </is>
       </c>
     </row>
@@ -2596,23 +2596,23 @@
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>올릭스</t>
         </is>
       </c>
       <c r="B58" s="11" t="n">
         <v>40</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>3108142875</v>
+        <v>2402711130</v>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>2.14%→3.71%</t>
+          <t>1.14%→2.32%</t>
         </is>
       </c>
       <c r="E58" s="13" t="inlineStr">
         <is>
-          <t>59→99</t>
+          <t>40→80</t>
         </is>
       </c>
       <c r="G58" s="14" t="inlineStr">
@@ -2640,23 +2640,23 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>올릭스</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B59" s="11" t="n">
         <v>40</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>2402711130</v>
+        <v>3108142875</v>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>1.14%→2.32%</t>
+          <t>2.14%→3.71%</t>
         </is>
       </c>
       <c r="E59" s="13" t="inlineStr">
         <is>
-          <t>40→80</t>
+          <t>59→99</t>
         </is>
       </c>
       <c r="G59" s="14" t="inlineStr">
@@ -2881,23 +2881,23 @@
       </c>
       <c r="G64" s="14" t="inlineStr">
         <is>
-          <t>대주전자재료</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H64" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I64" s="15" t="n">
-        <v>-1544789441</v>
+        <v>-1059142117</v>
       </c>
       <c r="J64" s="16" t="inlineStr">
         <is>
-          <t>1.52%→0.75%</t>
+          <t>1.23%→0.72%</t>
         </is>
       </c>
       <c r="K64" s="13" t="inlineStr">
         <is>
-          <t>50→25</t>
+          <t>60→35</t>
         </is>
       </c>
     </row>
@@ -2909,23 +2909,23 @@
       <c r="E65" s="17" t="n"/>
       <c r="G65" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>대주전자재료</t>
         </is>
       </c>
       <c r="H65" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I65" s="15" t="n">
-        <v>-1059142117</v>
+        <v>-1544789441</v>
       </c>
       <c r="J65" s="16" t="inlineStr">
         <is>
-          <t>1.23%→0.72%</t>
+          <t>1.52%→0.75%</t>
         </is>
       </c>
       <c r="K65" s="13" t="inlineStr">
         <is>
-          <t>60→35</t>
+          <t>50→25</t>
         </is>
       </c>
     </row>
@@ -3719,7 +3719,7 @@
     <row r="93" ht="19" customHeight="1">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,014억   ·   현금 69억(6.9%)      오늘 2026-10-28  vs  5일전 2026-10-21      매수 1종목  /  매도 3종목</t>
+          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,014억      오늘 2026-10-28  vs  5일전 2026-10-21      매수 1종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B93" s="4" t="n"/>
@@ -3857,23 +3857,23 @@
       <c r="E97" s="17" t="n"/>
       <c r="G97" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>와이바이오로직스</t>
         </is>
       </c>
       <c r="H97" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I97" s="15" t="n">
-        <v>-530626086</v>
+        <v>-84700878</v>
       </c>
       <c r="J97" s="16" t="inlineStr">
         <is>
-          <t>7.61%→5.06%</t>
+          <t>0.46%→0.25%</t>
         </is>
       </c>
       <c r="K97" s="13" t="inlineStr">
         <is>
-          <t>40→36</t>
+          <t>15→11</t>
         </is>
       </c>
     </row>
@@ -3885,23 +3885,23 @@
       <c r="E98" s="17" t="n"/>
       <c r="G98" s="14" t="inlineStr">
         <is>
-          <t>와이바이오로직스</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H98" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I98" s="15" t="n">
-        <v>-84700878</v>
+        <v>-530626086</v>
       </c>
       <c r="J98" s="16" t="inlineStr">
         <is>
-          <t>0.46%→0.25%</t>
+          <t>7.61%→5.06%</t>
         </is>
       </c>
       <c r="K98" s="13" t="inlineStr">
         <is>
-          <t>15→11</t>
+          <t>40→36</t>
         </is>
       </c>
     </row>
@@ -4625,7 +4625,7 @@
     <row r="119" ht="19" customHeight="1">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>■ TIGER 코스닥액티브  (미래에셋)      순자산 ≈ 292억   ·   현금 3억(1.1%)      오늘 2026-10-28  vs  5일전 2026-10-21      매수 12종목  /  매도 15종목</t>
+          <t>■ TIGER 코스닥액티브  (미래에셋)      순자산 ≈ 292억      오늘 2026-10-28  vs  5일전 2026-10-21      매수 12종목  /  매도 15종목</t>
         </is>
       </c>
       <c r="B119" s="4" t="n"/>
@@ -4846,23 +4846,23 @@
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>프로티나</t>
         </is>
       </c>
       <c r="B125" s="11" t="n">
         <v>11</v>
       </c>
       <c r="C125" s="11" t="n">
-        <v>267208890</v>
+        <v>226687612</v>
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>2.20%→3.12%</t>
+          <t>1.29%→2.07%</t>
         </is>
       </c>
       <c r="E125" s="13" t="inlineStr">
         <is>
-          <t>26→37</t>
+          <t>18→29</t>
         </is>
       </c>
       <c r="G125" s="14" t="inlineStr">
@@ -4890,23 +4890,23 @@
     <row r="126">
       <c r="A126" s="10" t="inlineStr">
         <is>
-          <t>프로티나</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="B126" s="11" t="n">
         <v>11</v>
       </c>
       <c r="C126" s="11" t="n">
-        <v>226687612</v>
+        <v>267208890</v>
       </c>
       <c r="D126" s="12" t="inlineStr">
         <is>
-          <t>1.29%→2.07%</t>
+          <t>2.20%→3.12%</t>
         </is>
       </c>
       <c r="E126" s="13" t="inlineStr">
         <is>
-          <t>18→29</t>
+          <t>26→37</t>
         </is>
       </c>
       <c r="G126" s="14" t="inlineStr">
@@ -4934,23 +4934,23 @@
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
         <is>
-          <t>선익시스템  (신규)</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="B127" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C127" s="11" t="n">
-        <v>319034027</v>
+        <v>85442011</v>
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.11%</t>
+          <t>0.69%→0.99%</t>
         </is>
       </c>
       <c r="E127" s="13" t="inlineStr">
         <is>
-          <t>0→9</t>
+          <t>21→30</t>
         </is>
       </c>
       <c r="G127" s="14" t="inlineStr">
@@ -4978,23 +4978,23 @@
     <row r="128">
       <c r="A128" s="10" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>선익시스템  (신규)</t>
         </is>
       </c>
       <c r="B128" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C128" s="11" t="n">
-        <v>85442011</v>
+        <v>319034027</v>
       </c>
       <c r="D128" s="12" t="inlineStr">
         <is>
-          <t>0.69%→0.99%</t>
+          <t>0.00%→1.11%</t>
         </is>
       </c>
       <c r="E128" s="13" t="inlineStr">
         <is>
-          <t>21→30</t>
+          <t>0→9</t>
         </is>
       </c>
       <c r="G128" s="14" t="inlineStr">
@@ -5110,23 +5110,23 @@
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>올릭스</t>
         </is>
       </c>
       <c r="B131" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C131" s="11" t="n">
-        <v>148023705</v>
+        <v>114427882</v>
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>5.84%→6.33%</t>
+          <t>2.39%→2.78%</t>
         </is>
       </c>
       <c r="E131" s="13" t="inlineStr">
         <is>
-          <t>34→37</t>
+          <t>18→21</t>
         </is>
       </c>
       <c r="G131" s="14" t="inlineStr">
@@ -5154,23 +5154,23 @@
     <row r="132">
       <c r="A132" s="10" t="inlineStr">
         <is>
-          <t>올릭스</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="B132" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C132" s="11" t="n">
-        <v>114427882</v>
+        <v>43889281</v>
       </c>
       <c r="D132" s="12" t="inlineStr">
         <is>
-          <t>2.39%→2.78%</t>
+          <t>0.87%→1.01%</t>
         </is>
       </c>
       <c r="E132" s="13" t="inlineStr">
         <is>
-          <t>18→21</t>
+          <t>17→20</t>
         </is>
       </c>
       <c r="G132" s="14" t="inlineStr">
@@ -5198,23 +5198,23 @@
     <row r="133">
       <c r="A133" s="10" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B133" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C133" s="11" t="n">
-        <v>43889281</v>
+        <v>148023705</v>
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>0.87%→1.01%</t>
+          <t>5.84%→6.33%</t>
         </is>
       </c>
       <c r="E133" s="13" t="inlineStr">
         <is>
-          <t>17→20</t>
+          <t>34→37</t>
         </is>
       </c>
       <c r="G133" s="14" t="inlineStr">
@@ -5326,7 +5326,7 @@
     <row r="138" ht="19" customHeight="1">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 55억   ·   현금 1억(1.7%)      오늘 2026-10-28  vs  5일전 2026-10-21      매수 4종목  /  매도 3종목</t>
+          <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 55억      오늘 2026-10-28  vs  5일전 2026-10-21      매수 4종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B138" s="4" t="n"/>

--- a/reports/pdf_rolling5_20261028.xlsx
+++ b/reports/pdf_rolling5_20261028.xlsx
@@ -1054,23 +1054,23 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>파크시스템스</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>2687059299</v>
+        <v>571968276</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>1.43%→1.92%</t>
+          <t>0.40%→0.51%</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>25→37</t>
+          <t>34→46</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -1098,23 +1098,23 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>파크시스템스</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>571968276</v>
+        <v>2687059299</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>0.40%→0.51%</t>
+          <t>1.43%→1.92%</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>34→46</t>
+          <t>25→37</t>
         </is>
       </c>
       <c r="G16" s="17" t="n"/>
@@ -1684,23 +1684,23 @@
       <c r="E33" s="17" t="n"/>
       <c r="G33" s="14" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="H33" s="15" t="n">
         <v>-22</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>-2734940287</v>
+        <v>-949845352</v>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
-          <t>3.76%→2.56%</t>
+          <t>7.43%→6.62%</t>
         </is>
       </c>
       <c r="K33" s="13" t="inlineStr">
         <is>
-          <t>81→59</t>
+          <t>462→440</t>
         </is>
       </c>
     </row>
@@ -1712,23 +1712,23 @@
       <c r="E34" s="17" t="n"/>
       <c r="G34" s="14" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="H34" s="15" t="n">
         <v>-22</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-949845352</v>
+        <v>-2734940287</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
-          <t>7.43%→6.62%</t>
+          <t>3.76%→2.56%</t>
         </is>
       </c>
       <c r="K34" s="13" t="inlineStr">
         <is>
-          <t>462→440</t>
+          <t>81→59</t>
         </is>
       </c>
     </row>
@@ -2200,18 +2200,18 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>알멕  (신규)</t>
+          <t>엘리스  (신규)</t>
         </is>
       </c>
       <c r="B49" s="11" t="n">
         <v>150</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>6195732757</v>
+        <v>8015667098</v>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>0.00%→2.99%</t>
+          <t>0.00%→3.87%</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
@@ -2244,18 +2244,18 @@
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>엘리스  (신규)</t>
+          <t>알멕  (신규)</t>
         </is>
       </c>
       <c r="B50" s="11" t="n">
         <v>150</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>8015667098</v>
+        <v>6195732757</v>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>0.00%→3.87%</t>
+          <t>0.00%→2.99%</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
@@ -2881,23 +2881,23 @@
       </c>
       <c r="G64" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>대주전자재료</t>
         </is>
       </c>
       <c r="H64" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I64" s="15" t="n">
-        <v>-1059142117</v>
+        <v>-1544789441</v>
       </c>
       <c r="J64" s="16" t="inlineStr">
         <is>
-          <t>1.23%→0.72%</t>
+          <t>1.52%→0.75%</t>
         </is>
       </c>
       <c r="K64" s="13" t="inlineStr">
         <is>
-          <t>60→35</t>
+          <t>50→25</t>
         </is>
       </c>
     </row>
@@ -2909,23 +2909,23 @@
       <c r="E65" s="17" t="n"/>
       <c r="G65" s="14" t="inlineStr">
         <is>
-          <t>대주전자재료</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H65" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I65" s="15" t="n">
-        <v>-1544789441</v>
+        <v>-1059142117</v>
       </c>
       <c r="J65" s="16" t="inlineStr">
         <is>
-          <t>1.52%→0.75%</t>
+          <t>1.23%→0.72%</t>
         </is>
       </c>
       <c r="K65" s="13" t="inlineStr">
         <is>
-          <t>50→25</t>
+          <t>60→35</t>
         </is>
       </c>
     </row>
@@ -3857,23 +3857,23 @@
       <c r="E97" s="17" t="n"/>
       <c r="G97" s="14" t="inlineStr">
         <is>
-          <t>와이바이오로직스</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H97" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I97" s="15" t="n">
-        <v>-84700878</v>
+        <v>-530626086</v>
       </c>
       <c r="J97" s="16" t="inlineStr">
         <is>
-          <t>0.46%→0.25%</t>
+          <t>7.61%→5.06%</t>
         </is>
       </c>
       <c r="K97" s="13" t="inlineStr">
         <is>
-          <t>15→11</t>
+          <t>40→36</t>
         </is>
       </c>
     </row>
@@ -3885,23 +3885,23 @@
       <c r="E98" s="17" t="n"/>
       <c r="G98" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>와이바이오로직스</t>
         </is>
       </c>
       <c r="H98" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I98" s="15" t="n">
-        <v>-530626086</v>
+        <v>-84700878</v>
       </c>
       <c r="J98" s="16" t="inlineStr">
         <is>
-          <t>7.61%→5.06%</t>
+          <t>0.46%→0.25%</t>
         </is>
       </c>
       <c r="K98" s="13" t="inlineStr">
         <is>
-          <t>40→36</t>
+          <t>15→11</t>
         </is>
       </c>
     </row>
@@ -4714,18 +4714,18 @@
     <row r="122">
       <c r="A122" s="10" t="inlineStr">
         <is>
-          <t>파인엠텍  (신규)</t>
+          <t>루닛  (신규)</t>
         </is>
       </c>
       <c r="B122" s="11" t="n">
         <v>61</v>
       </c>
       <c r="C122" s="11" t="n">
-        <v>254242081</v>
+        <v>376226918</v>
       </c>
       <c r="D122" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.88%</t>
+          <t>0.00%→1.30%</t>
         </is>
       </c>
       <c r="E122" s="13" t="inlineStr">
@@ -4758,18 +4758,18 @@
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>루닛  (신규)</t>
+          <t>파인엠텍  (신규)</t>
         </is>
       </c>
       <c r="B123" s="11" t="n">
         <v>61</v>
       </c>
       <c r="C123" s="11" t="n">
-        <v>376226918</v>
+        <v>254242081</v>
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.30%</t>
+          <t>0.00%→0.88%</t>
         </is>
       </c>
       <c r="E123" s="13" t="inlineStr">
@@ -5110,23 +5110,23 @@
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
         <is>
-          <t>올릭스</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="B131" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C131" s="11" t="n">
-        <v>114427882</v>
+        <v>43889281</v>
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>2.39%→2.78%</t>
+          <t>0.87%→1.01%</t>
         </is>
       </c>
       <c r="E131" s="13" t="inlineStr">
         <is>
-          <t>18→21</t>
+          <t>17→20</t>
         </is>
       </c>
       <c r="G131" s="14" t="inlineStr">
@@ -5154,23 +5154,23 @@
     <row r="132">
       <c r="A132" s="10" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>올릭스</t>
         </is>
       </c>
       <c r="B132" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C132" s="11" t="n">
-        <v>43889281</v>
+        <v>114427882</v>
       </c>
       <c r="D132" s="12" t="inlineStr">
         <is>
-          <t>0.87%→1.01%</t>
+          <t>2.39%→2.78%</t>
         </is>
       </c>
       <c r="E132" s="13" t="inlineStr">
         <is>
-          <t>17→20</t>
+          <t>18→21</t>
         </is>
       </c>
       <c r="G132" s="14" t="inlineStr">

--- a/reports/pdf_rolling5_20261028.xlsx
+++ b/reports/pdf_rolling5_20261028.xlsx
@@ -2200,18 +2200,18 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>엘리스  (신규)</t>
+          <t>알멕  (신규)</t>
         </is>
       </c>
       <c r="B49" s="11" t="n">
         <v>150</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>8015667098</v>
+        <v>6195732757</v>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>0.00%→3.87%</t>
+          <t>0.00%→2.99%</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
@@ -2244,18 +2244,18 @@
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>알멕  (신규)</t>
+          <t>엘리스  (신규)</t>
         </is>
       </c>
       <c r="B50" s="11" t="n">
         <v>150</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>6195732757</v>
+        <v>8015667098</v>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>0.00%→2.99%</t>
+          <t>0.00%→3.87%</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
@@ -2376,18 +2376,18 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>디케이티  (신규)</t>
+          <t>엘티씨  (신규)</t>
         </is>
       </c>
       <c r="B53" s="11" t="n">
         <v>99</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>1680306592</v>
+        <v>2205402402</v>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.81%</t>
+          <t>0.00%→1.06%</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
@@ -2420,18 +2420,18 @@
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>엘티씨  (신규)</t>
+          <t>디케이티  (신규)</t>
         </is>
       </c>
       <c r="B54" s="11" t="n">
         <v>99</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>2205402402</v>
+        <v>1680306592</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.06%</t>
+          <t>0.00%→0.81%</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
@@ -2596,23 +2596,23 @@
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>올릭스</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B58" s="11" t="n">
         <v>40</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>2402711130</v>
+        <v>3108142875</v>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>1.14%→2.32%</t>
+          <t>2.14%→3.71%</t>
         </is>
       </c>
       <c r="E58" s="13" t="inlineStr">
         <is>
-          <t>40→80</t>
+          <t>59→99</t>
         </is>
       </c>
       <c r="G58" s="14" t="inlineStr">
@@ -2640,23 +2640,23 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>올릭스</t>
         </is>
       </c>
       <c r="B59" s="11" t="n">
         <v>40</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>3108142875</v>
+        <v>2402711130</v>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>2.14%→3.71%</t>
+          <t>1.14%→2.32%</t>
         </is>
       </c>
       <c r="E59" s="13" t="inlineStr">
         <is>
-          <t>59→99</t>
+          <t>40→80</t>
         </is>
       </c>
       <c r="G59" s="14" t="inlineStr">
@@ -4846,23 +4846,23 @@
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>프로티나</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="B125" s="11" t="n">
         <v>11</v>
       </c>
       <c r="C125" s="11" t="n">
-        <v>226687612</v>
+        <v>267208890</v>
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>1.29%→2.07%</t>
+          <t>2.20%→3.12%</t>
         </is>
       </c>
       <c r="E125" s="13" t="inlineStr">
         <is>
-          <t>18→29</t>
+          <t>26→37</t>
         </is>
       </c>
       <c r="G125" s="14" t="inlineStr">
@@ -4890,23 +4890,23 @@
     <row r="126">
       <c r="A126" s="10" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>프로티나</t>
         </is>
       </c>
       <c r="B126" s="11" t="n">
         <v>11</v>
       </c>
       <c r="C126" s="11" t="n">
-        <v>267208890</v>
+        <v>226687612</v>
       </c>
       <c r="D126" s="12" t="inlineStr">
         <is>
-          <t>2.20%→3.12%</t>
+          <t>1.29%→2.07%</t>
         </is>
       </c>
       <c r="E126" s="13" t="inlineStr">
         <is>
-          <t>26→37</t>
+          <t>18→29</t>
         </is>
       </c>
       <c r="G126" s="14" t="inlineStr">
@@ -5110,23 +5110,23 @@
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B131" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C131" s="11" t="n">
-        <v>43889281</v>
+        <v>148023705</v>
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>0.87%→1.01%</t>
+          <t>5.84%→6.33%</t>
         </is>
       </c>
       <c r="E131" s="13" t="inlineStr">
         <is>
-          <t>17→20</t>
+          <t>34→37</t>
         </is>
       </c>
       <c r="G131" s="14" t="inlineStr">
@@ -5198,23 +5198,23 @@
     <row r="133">
       <c r="A133" s="10" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="B133" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C133" s="11" t="n">
-        <v>148023705</v>
+        <v>43889281</v>
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>5.84%→6.33%</t>
+          <t>0.87%→1.01%</t>
         </is>
       </c>
       <c r="E133" s="13" t="inlineStr">
         <is>
-          <t>34→37</t>
+          <t>17→20</t>
         </is>
       </c>
       <c r="G133" s="14" t="inlineStr">

--- a/reports/pdf_rolling5_20261028.xlsx
+++ b/reports/pdf_rolling5_20261028.xlsx
@@ -3857,23 +3857,23 @@
       <c r="E97" s="17" t="n"/>
       <c r="G97" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>와이바이오로직스</t>
         </is>
       </c>
       <c r="H97" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I97" s="15" t="n">
-        <v>-530626086</v>
+        <v>-84700878</v>
       </c>
       <c r="J97" s="16" t="inlineStr">
         <is>
-          <t>7.61%→5.06%</t>
+          <t>0.46%→0.25%</t>
         </is>
       </c>
       <c r="K97" s="13" t="inlineStr">
         <is>
-          <t>40→36</t>
+          <t>15→11</t>
         </is>
       </c>
     </row>
@@ -3885,23 +3885,23 @@
       <c r="E98" s="17" t="n"/>
       <c r="G98" s="14" t="inlineStr">
         <is>
-          <t>와이바이오로직스</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H98" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I98" s="15" t="n">
-        <v>-84700878</v>
+        <v>-530626086</v>
       </c>
       <c r="J98" s="16" t="inlineStr">
         <is>
-          <t>0.46%→0.25%</t>
+          <t>7.61%→5.06%</t>
         </is>
       </c>
       <c r="K98" s="13" t="inlineStr">
         <is>
-          <t>15→11</t>
+          <t>40→36</t>
         </is>
       </c>
     </row>
@@ -4714,18 +4714,18 @@
     <row r="122">
       <c r="A122" s="10" t="inlineStr">
         <is>
-          <t>루닛  (신규)</t>
+          <t>파인엠텍  (신규)</t>
         </is>
       </c>
       <c r="B122" s="11" t="n">
         <v>61</v>
       </c>
       <c r="C122" s="11" t="n">
-        <v>376226918</v>
+        <v>254242081</v>
       </c>
       <c r="D122" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.30%</t>
+          <t>0.00%→0.88%</t>
         </is>
       </c>
       <c r="E122" s="13" t="inlineStr">
@@ -4758,18 +4758,18 @@
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>파인엠텍  (신규)</t>
+          <t>루닛  (신규)</t>
         </is>
       </c>
       <c r="B123" s="11" t="n">
         <v>61</v>
       </c>
       <c r="C123" s="11" t="n">
-        <v>254242081</v>
+        <v>376226918</v>
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.88%</t>
+          <t>0.00%→1.30%</t>
         </is>
       </c>
       <c r="E123" s="13" t="inlineStr">
@@ -4846,23 +4846,23 @@
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>프로티나</t>
         </is>
       </c>
       <c r="B125" s="11" t="n">
         <v>11</v>
       </c>
       <c r="C125" s="11" t="n">
-        <v>267208890</v>
+        <v>226687612</v>
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>2.20%→3.12%</t>
+          <t>1.29%→2.07%</t>
         </is>
       </c>
       <c r="E125" s="13" t="inlineStr">
         <is>
-          <t>26→37</t>
+          <t>18→29</t>
         </is>
       </c>
       <c r="G125" s="14" t="inlineStr">
@@ -4890,23 +4890,23 @@
     <row r="126">
       <c r="A126" s="10" t="inlineStr">
         <is>
-          <t>프로티나</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="B126" s="11" t="n">
         <v>11</v>
       </c>
       <c r="C126" s="11" t="n">
-        <v>226687612</v>
+        <v>267208890</v>
       </c>
       <c r="D126" s="12" t="inlineStr">
         <is>
-          <t>1.29%→2.07%</t>
+          <t>2.20%→3.12%</t>
         </is>
       </c>
       <c r="E126" s="13" t="inlineStr">
         <is>
-          <t>18→29</t>
+          <t>26→37</t>
         </is>
       </c>
       <c r="G126" s="14" t="inlineStr">
@@ -5110,23 +5110,23 @@
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="B131" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C131" s="11" t="n">
-        <v>148023705</v>
+        <v>43889281</v>
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>5.84%→6.33%</t>
+          <t>0.87%→1.01%</t>
         </is>
       </c>
       <c r="E131" s="13" t="inlineStr">
         <is>
-          <t>34→37</t>
+          <t>17→20</t>
         </is>
       </c>
       <c r="G131" s="14" t="inlineStr">
@@ -5154,23 +5154,23 @@
     <row r="132">
       <c r="A132" s="10" t="inlineStr">
         <is>
-          <t>올릭스</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B132" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C132" s="11" t="n">
-        <v>114427882</v>
+        <v>148023705</v>
       </c>
       <c r="D132" s="12" t="inlineStr">
         <is>
-          <t>2.39%→2.78%</t>
+          <t>5.84%→6.33%</t>
         </is>
       </c>
       <c r="E132" s="13" t="inlineStr">
         <is>
-          <t>18→21</t>
+          <t>34→37</t>
         </is>
       </c>
       <c r="G132" s="14" t="inlineStr">
@@ -5198,23 +5198,23 @@
     <row r="133">
       <c r="A133" s="10" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>올릭스</t>
         </is>
       </c>
       <c r="B133" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C133" s="11" t="n">
-        <v>43889281</v>
+        <v>114427882</v>
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>0.87%→1.01%</t>
+          <t>2.39%→2.78%</t>
         </is>
       </c>
       <c r="E133" s="13" t="inlineStr">
         <is>
-          <t>17→20</t>
+          <t>18→21</t>
         </is>
       </c>
       <c r="G133" s="14" t="inlineStr">
